--- a/output/Shandong/枣庄市_news.xlsx
+++ b/output/Shandong/枣庄市_news.xlsx
@@ -551,9 +551,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>True</t>
@@ -565,14 +563,12 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9331</v>
+        <v>9514</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/3c66ac1100d4473482117482e2eb21d8/detail</t>
@@ -621,9 +617,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>True</t>
@@ -635,14 +629,12 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>8945</v>
+        <v>9117</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/9e2aead198a54ab59aac5c1d02499341/detail</t>
@@ -691,9 +683,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>True</t>
@@ -705,14 +695,12 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>9041</v>
+        <v>9207</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ef4ec15d8d8e457b81f3a487cd7316ed/detail</t>
@@ -761,9 +749,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>True</t>
@@ -775,14 +761,12 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8928</v>
+        <v>9100</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/f4039df7fd0547c3ad16e15bf21f2986/detail</t>
@@ -831,9 +815,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>True</t>
@@ -845,14 +827,12 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9115</v>
+        <v>9281</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/023c1a3711174fcfb51f8e6434b9ee11/detail</t>
@@ -901,9 +881,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>True</t>
@@ -915,14 +893,12 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>9043</v>
+        <v>9223</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/307b0329e71041d68631ca0220fc2460/detail</t>
@@ -971,9 +947,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>True</t>
@@ -985,14 +959,12 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9413</v>
+        <v>9594</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/f2c074f6f1164713bdd054de71d8c210/detail</t>
@@ -1041,9 +1013,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>True</t>
@@ -1055,14 +1025,12 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9285</v>
+        <v>9459</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/d53ec35a39b543d5a4f0e0a3d673b601/detail</t>
@@ -1111,9 +1079,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>True</t>
@@ -1125,14 +1091,12 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9629</v>
+        <v>9797</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/1c9827db4b0c4e31bb8a4de2c8aee9ea/detail</t>
@@ -1181,9 +1145,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>True</t>
@@ -1195,14 +1157,12 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>10051</v>
+        <v>10233</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/1b0bb7d099374fd2a1adb71434196a8a/detail</t>
@@ -1251,9 +1211,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>True</t>
@@ -1265,14 +1223,12 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>12316</v>
+        <v>12475</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/41923e9253c549c0b50d88db436d970c/detail</t>
@@ -1321,9 +1277,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>True</t>
@@ -1335,14 +1289,12 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12264</v>
+        <v>12292</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/d740c1cebe9946f4a6c6a96e5be5fa7c/detail</t>
@@ -1391,9 +1343,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>True</t>
@@ -1405,14 +1355,12 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>13415</v>
+        <v>13426</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/6d5652c2285b4c069c8ede92aa65aaf8/detail</t>
@@ -1461,9 +1409,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>True</t>
@@ -1475,14 +1421,12 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>13765</v>
+        <v>13768</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/2650cb4a842340fe84d896aefed59421/detail</t>
@@ -1531,9 +1475,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>True</t>
@@ -1545,14 +1487,12 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>10871</v>
+        <v>10879</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/59ee70810dd44530b87ed05c155bf433/detail</t>
@@ -1601,9 +1541,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>True</t>
@@ -1615,14 +1553,12 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/53d3abf676884e2eba77d34d46c957e7/detail</t>
@@ -1671,9 +1607,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>True</t>
@@ -1685,14 +1619,12 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2546</v>
+        <v>2577</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/74cd6e44765b4f32a00cfb9befe94de9/detail</t>
@@ -1741,9 +1673,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>True</t>
@@ -1755,14 +1685,12 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/71142c46912b4f7aa221941377718eff/detail</t>
@@ -1811,9 +1739,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>True</t>
@@ -1825,14 +1751,12 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/144eaca06bc740bfb464869bafbc337d/detail</t>
@@ -1881,9 +1805,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>True</t>
@@ -1895,14 +1817,12 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/f3bc6de214fb496bb7368a4b99725cb3/detail</t>
@@ -1951,9 +1871,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>True</t>
@@ -1965,14 +1883,12 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/6ada0c7c9c3e4ddc9b63b973d8824739/detail</t>
@@ -2021,9 +1937,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>True</t>
@@ -2035,14 +1949,12 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/2ddad108fd784213b79a0cbb0ab3d44d/detail</t>
@@ -2091,9 +2003,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>True</t>
@@ -2105,14 +2015,12 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>318</v>
+        <v>421</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/e0c7cbd4ac604c8da0e66cec12dfa427/detail</t>
@@ -2161,9 +2069,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>True</t>
@@ -2175,14 +2081,12 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6653</v>
+        <v>6732</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/c9a01033173d476b8cc06e816b8cf15c/detail</t>
@@ -2231,9 +2135,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>True</t>
@@ -2245,14 +2147,12 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1005</v>
+        <v>1026</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/db523ab564f9450eb4086ec0ea4ff821/detail</t>
@@ -2301,9 +2201,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>True</t>
@@ -2315,14 +2213,12 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/1da1a1d48775432cb0d693fa92c05764/detail</t>
@@ -2371,9 +2267,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>True</t>
@@ -2385,14 +2279,12 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/7b79d91f39cd467ba72093d7b654cb87/detail</t>
@@ -2441,9 +2333,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>True</t>
@@ -2455,14 +2345,12 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/dc7629ed12aa4c4d8a2b32c93e52890f/detail</t>
@@ -2511,9 +2399,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>True</t>
@@ -2525,14 +2411,12 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/02271a74fed44615a3fa2425808d8423/detail</t>
@@ -2581,9 +2465,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>True</t>
@@ -2595,14 +2477,12 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>6005</v>
+        <v>6032</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/23d5af65393e4527aba4e36d792dd054/detail</t>
@@ -2651,9 +2531,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>True</t>
@@ -2665,14 +2543,12 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>9885</v>
+        <v>10014</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/3e3f672979ca4e12bccec7839488583f/detail</t>
@@ -2721,9 +2597,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>True</t>
@@ -2735,14 +2609,12 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1641</v>
+        <v>1647</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/11bc57b5ba1442028df8557a88c64c19/detail</t>
@@ -2791,9 +2663,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>True</t>
@@ -2805,14 +2675,12 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3280</v>
+        <v>3377</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/be6be2477a774daf8cdcdf01c8c87066/detail</t>
@@ -2861,9 +2729,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>True</t>
@@ -2875,14 +2741,12 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4406</v>
+        <v>4425</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/cf8d1381c117417d967ac67b0de24ac3/detail</t>
@@ -2931,9 +2795,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>True</t>
@@ -2945,14 +2807,12 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/b9575e4aa5fd4d1dbece660ef9350eac/detail</t>
@@ -3001,9 +2861,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>True</t>
@@ -3015,14 +2873,12 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/8cf900b2928e4f8781495875d3901f30/detail</t>
@@ -3071,9 +2927,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>True</t>
@@ -3085,14 +2939,12 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2182</v>
+        <v>2189</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/b401f6bf628f4429bd134ccac46aab0d/detail</t>
@@ -3141,9 +2993,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>True</t>
@@ -3155,14 +3005,12 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4640</v>
+        <v>4703</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/33d4142184df4af382e6af257e21ca75/detail</t>
